--- a/output/docs/DOC_066_FUZZ_report.xlsx
+++ b/output/docs/DOC_066_FUZZ_report.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,39 +529,76 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>CWE-190</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>/api/qty/99999999999999</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>integer far out of range -&gt; unhandled server error (HTTP 500)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>FND-0014</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>CWE-20</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>POST /api/items (quantity)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>out-of-range integer causes unhandled HTTP 500</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>/api/qty/abc</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>wrong type where integer expected -&gt; unhandled server error (HTTP 500)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Remediate / upgrade; verified on retest.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Total findings: 1</t>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total findings: 2</t>
         </is>
       </c>
     </row>
